--- a/2026_dashboard.xlsx
+++ b/2026_dashboard.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\■ 26_NE능률_업무폴더_온라인유통\26년 월별 계획 및 실적\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwchoi\.gemini\antigravity\scratch\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8166F9A8-8BC3-4838-BABF-9B9A192704A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6AA15F5-D1ED-4D76-9CF4-085CA309DE6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30285" yWindow="1275" windowWidth="25770" windowHeight="13380" xr2:uid="{372AB101-DDC1-4D0A-9680-BFBF2765E290}"/>
   </bookViews>
@@ -488,27 +488,39 @@
     <xf numFmtId="41" fontId="5" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -526,18 +538,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -927,7 +927,7 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="28" t="s">
         <v>26</v>
       </c>
       <c r="B2" s="6">
@@ -968,48 +968,48 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="42">
+      <c r="B3" s="29">
         <v>315669765</v>
       </c>
-      <c r="C3" s="42">
+      <c r="C3" s="29">
         <v>307671200</v>
       </c>
-      <c r="D3" s="42">
+      <c r="D3" s="29">
         <v>207081610</v>
       </c>
-      <c r="E3" s="42">
-        <v>0</v>
-      </c>
-      <c r="F3" s="42">
-        <v>0</v>
-      </c>
-      <c r="G3" s="42">
-        <v>0</v>
-      </c>
-      <c r="H3" s="42">
-        <v>0</v>
-      </c>
-      <c r="I3" s="42">
-        <v>0</v>
-      </c>
-      <c r="J3" s="42">
-        <v>0</v>
-      </c>
-      <c r="K3" s="42">
-        <v>0</v>
-      </c>
-      <c r="L3" s="42">
-        <v>0</v>
-      </c>
-      <c r="M3" s="42">
+      <c r="E3" s="29">
+        <v>0</v>
+      </c>
+      <c r="F3" s="29">
+        <v>0</v>
+      </c>
+      <c r="G3" s="29">
+        <v>0</v>
+      </c>
+      <c r="H3" s="29">
+        <v>0</v>
+      </c>
+      <c r="I3" s="29">
+        <v>2222222</v>
+      </c>
+      <c r="J3" s="29">
+        <v>0</v>
+      </c>
+      <c r="K3" s="29">
+        <v>0</v>
+      </c>
+      <c r="L3" s="29">
+        <v>0</v>
+      </c>
+      <c r="M3" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="28" t="s">
         <v>28</v>
       </c>
       <c r="B4" s="6">
@@ -1050,48 +1050,48 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="42">
+      <c r="B5" s="29">
         <v>124437728</v>
       </c>
-      <c r="C5" s="42">
+      <c r="C5" s="29">
         <v>90613312</v>
       </c>
-      <c r="D5" s="42">
+      <c r="D5" s="29">
         <v>75975344</v>
       </c>
-      <c r="E5" s="42">
-        <v>0</v>
-      </c>
-      <c r="F5" s="42">
-        <v>0</v>
-      </c>
-      <c r="G5" s="42">
-        <v>0</v>
-      </c>
-      <c r="H5" s="42">
-        <v>0</v>
-      </c>
-      <c r="I5" s="42">
-        <v>0</v>
-      </c>
-      <c r="J5" s="42">
-        <v>0</v>
-      </c>
-      <c r="K5" s="42">
-        <v>0</v>
-      </c>
-      <c r="L5" s="42">
-        <v>0</v>
-      </c>
-      <c r="M5" s="42">
+      <c r="E5" s="29">
+        <v>0</v>
+      </c>
+      <c r="F5" s="29">
+        <v>0</v>
+      </c>
+      <c r="G5" s="29">
+        <v>0</v>
+      </c>
+      <c r="H5" s="29">
+        <v>0</v>
+      </c>
+      <c r="I5" s="29">
+        <v>0</v>
+      </c>
+      <c r="J5" s="29">
+        <v>0</v>
+      </c>
+      <c r="K5" s="29">
+        <v>0</v>
+      </c>
+      <c r="L5" s="29">
+        <v>0</v>
+      </c>
+      <c r="M5" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="28" t="s">
         <v>30</v>
       </c>
       <c r="B6" s="6">
@@ -1109,66 +1109,66 @@
       <c r="F6" s="6">
         <v>131985130.27563205</v>
       </c>
-      <c r="G6" s="43">
+      <c r="G6" s="30">
         <v>394786021.99495518</v>
       </c>
-      <c r="H6" s="43">
+      <c r="H6" s="30">
         <v>356113852.83867455</v>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="30">
         <v>633076526.71854794</v>
       </c>
-      <c r="J6" s="43">
+      <c r="J6" s="30">
         <v>197086680.85687456</v>
       </c>
-      <c r="K6" s="43">
+      <c r="K6" s="30">
         <v>215347577.16981396</v>
       </c>
-      <c r="L6" s="43">
+      <c r="L6" s="30">
         <v>356618433.32053941</v>
       </c>
-      <c r="M6" s="43">
+      <c r="M6" s="30">
         <v>466482667.94791228</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="42">
+      <c r="B7" s="29">
         <v>165219300</v>
       </c>
-      <c r="C7" s="42">
+      <c r="C7" s="29">
         <v>732995100</v>
       </c>
-      <c r="D7" s="42">
+      <c r="D7" s="29">
         <v>32472600</v>
       </c>
-      <c r="E7" s="42">
-        <v>0</v>
-      </c>
-      <c r="F7" s="42">
-        <v>0</v>
-      </c>
-      <c r="G7" s="44">
-        <v>0</v>
-      </c>
-      <c r="H7" s="44">
-        <v>0</v>
-      </c>
-      <c r="I7" s="44">
-        <v>0</v>
-      </c>
-      <c r="J7" s="44">
-        <v>0</v>
-      </c>
-      <c r="K7" s="44">
-        <v>0</v>
-      </c>
-      <c r="L7" s="44">
-        <v>0</v>
-      </c>
-      <c r="M7" s="44">
+      <c r="E7" s="29">
+        <v>0</v>
+      </c>
+      <c r="F7" s="29">
+        <v>0</v>
+      </c>
+      <c r="G7" s="31">
+        <v>0</v>
+      </c>
+      <c r="H7" s="31">
+        <v>0</v>
+      </c>
+      <c r="I7" s="31">
+        <v>0</v>
+      </c>
+      <c r="J7" s="31">
+        <v>0</v>
+      </c>
+      <c r="K7" s="31">
+        <v>0</v>
+      </c>
+      <c r="L7" s="31">
+        <v>0</v>
+      </c>
+      <c r="M7" s="31">
         <v>0</v>
       </c>
     </row>
@@ -1205,43 +1205,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-      <c r="AA1" s="30"/>
-      <c r="AB1" s="30"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
+      <c r="V1" s="32"/>
+      <c r="W1" s="32"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="32"/>
+      <c r="AA1" s="32"/>
+      <c r="AB1" s="32"/>
     </row>
     <row r="2" spans="2:29" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:29" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="32"/>
+      <c r="B3" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="33"/>
+      <c r="D3" s="34"/>
       <c r="E3" s="11" t="s">
         <v>9</v>
       </c>
@@ -1316,10 +1316,10 @@
       </c>
     </row>
     <row r="4" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="37" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="24" t="s">
@@ -1415,8 +1415,8 @@
       </c>
     </row>
     <row r="5" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="39"/>
-      <c r="C5" s="29"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="38"/>
       <c r="D5" s="25" t="s">
         <v>25</v>
       </c>
@@ -1483,7 +1483,7 @@
       <c r="AC5" s="4"/>
     </row>
     <row r="6" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="39"/>
+      <c r="B6" s="43"/>
       <c r="C6" s="9" t="s">
         <v>20</v>
       </c>
@@ -1589,8 +1589,8 @@
       <c r="AC6" s="4"/>
     </row>
     <row r="7" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="39"/>
-      <c r="C7" s="28" t="s">
+      <c r="B7" s="43"/>
+      <c r="C7" s="37" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="24" t="s">
@@ -1686,8 +1686,8 @@
       </c>
     </row>
     <row r="8" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="39"/>
-      <c r="C8" s="29"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="38"/>
       <c r="D8" s="25" t="s">
         <v>25</v>
       </c>
@@ -1754,7 +1754,7 @@
       <c r="AC8" s="4"/>
     </row>
     <row r="9" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="39"/>
+      <c r="B9" s="43"/>
       <c r="C9" s="9" t="s">
         <v>20</v>
       </c>
@@ -1860,8 +1860,8 @@
       <c r="AC9" s="4"/>
     </row>
     <row r="10" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="39"/>
-      <c r="C10" s="28" t="s">
+      <c r="B10" s="43"/>
+      <c r="C10" s="37" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="24" t="s">
@@ -1957,8 +1957,8 @@
       </c>
     </row>
     <row r="11" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="39"/>
-      <c r="C11" s="29"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="38"/>
       <c r="D11" s="25" t="s">
         <v>25</v>
       </c>
@@ -2024,7 +2024,7 @@
       </c>
     </row>
     <row r="12" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="40"/>
+      <c r="B12" s="44"/>
       <c r="C12" s="2" t="s">
         <v>20</v>
       </c>
@@ -2129,11 +2129,11 @@
       </c>
     </row>
     <row r="13" spans="2:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="37"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="41"/>
       <c r="E13" s="15">
         <f>E4+E7+E10</f>
         <v>606065365.68358994</v>
@@ -2232,11 +2232,11 @@
       </c>
     </row>
     <row r="14" spans="2:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="33"/>
-      <c r="D14" s="34"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="36"/>
       <c r="E14" s="26">
         <f>E5+E8+E11</f>
         <v>614044688</v>

--- a/2026_dashboard.xlsx
+++ b/2026_dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwchoi\.gemini\antigravity\scratch\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D71230-10D1-43AE-BDBB-6E5F215204E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D475C858-3DCE-4479-9A4C-C8AD769FEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2145" yWindow="1050" windowWidth="25770" windowHeight="13380" xr2:uid="{372AB101-DDC1-4D0A-9680-BFBF2765E290}"/>
   </bookViews>
@@ -222,7 +222,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -259,12 +259,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC66"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -403,7 +397,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -491,15 +485,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -538,6 +523,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -971,40 +962,40 @@
       <c r="A3" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="29">
+      <c r="B3" s="3">
         <v>315669765</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="3">
         <v>307671200</v>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="3">
         <v>207081610</v>
       </c>
-      <c r="E3" s="29">
-        <v>0</v>
-      </c>
-      <c r="F3" s="29">
-        <v>0</v>
-      </c>
-      <c r="G3" s="29">
-        <v>0</v>
-      </c>
-      <c r="H3" s="29">
-        <v>0</v>
-      </c>
-      <c r="I3" s="29">
-        <v>0</v>
-      </c>
-      <c r="J3" s="29">
-        <v>0</v>
-      </c>
-      <c r="K3" s="29">
-        <v>0</v>
-      </c>
-      <c r="L3" s="29">
-        <v>0</v>
-      </c>
-      <c r="M3" s="29">
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>22222</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1053,40 +1044,40 @@
       <c r="A5" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="3">
         <v>124437728</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="3">
         <v>90613312</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="3">
         <v>75975344</v>
       </c>
-      <c r="E5" s="29">
-        <v>0</v>
-      </c>
-      <c r="F5" s="29">
-        <v>0</v>
-      </c>
-      <c r="G5" s="29">
-        <v>0</v>
-      </c>
-      <c r="H5" s="29">
-        <v>0</v>
-      </c>
-      <c r="I5" s="29">
-        <v>0</v>
-      </c>
-      <c r="J5" s="29">
-        <v>0</v>
-      </c>
-      <c r="K5" s="29">
-        <v>0</v>
-      </c>
-      <c r="L5" s="29">
-        <v>0</v>
-      </c>
-      <c r="M5" s="29">
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>22222</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1109,25 +1100,25 @@
       <c r="F6" s="6">
         <v>131985130.27563205</v>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="42">
         <v>394786021.99495518</v>
       </c>
-      <c r="H6" s="30">
+      <c r="H6" s="42">
         <v>356113852.83867455</v>
       </c>
-      <c r="I6" s="30">
+      <c r="I6" s="42">
         <v>633076526.71854794</v>
       </c>
-      <c r="J6" s="30">
+      <c r="J6" s="42">
         <v>197086680.85687456</v>
       </c>
-      <c r="K6" s="30">
+      <c r="K6" s="42">
         <v>215347577.16981396</v>
       </c>
-      <c r="L6" s="30">
+      <c r="L6" s="42">
         <v>356618433.32053941</v>
       </c>
-      <c r="M6" s="30">
+      <c r="M6" s="42">
         <v>466482667.94791228</v>
       </c>
     </row>
@@ -1135,40 +1126,40 @@
       <c r="A7" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="3">
         <v>165219300</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="3">
         <v>732995100</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="3">
         <v>32472600</v>
       </c>
-      <c r="E7" s="29">
-        <v>0</v>
-      </c>
-      <c r="F7" s="29">
-        <v>0</v>
-      </c>
-      <c r="G7" s="31">
-        <v>0</v>
-      </c>
-      <c r="H7" s="31">
-        <v>0</v>
-      </c>
-      <c r="I7" s="31">
-        <v>0</v>
-      </c>
-      <c r="J7" s="31">
-        <v>0</v>
-      </c>
-      <c r="K7" s="31">
-        <v>0</v>
-      </c>
-      <c r="L7" s="31">
-        <v>0</v>
-      </c>
-      <c r="M7" s="31">
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="43">
+        <v>22222</v>
+      </c>
+      <c r="H7" s="43">
+        <v>0</v>
+      </c>
+      <c r="I7" s="43">
+        <v>0</v>
+      </c>
+      <c r="J7" s="43">
+        <v>0</v>
+      </c>
+      <c r="K7" s="43">
+        <v>0</v>
+      </c>
+      <c r="L7" s="43">
+        <v>0</v>
+      </c>
+      <c r="M7" s="43">
         <v>0</v>
       </c>
     </row>
@@ -1205,43 +1196,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="32"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+      <c r="AB1" s="29"/>
     </row>
     <row r="2" spans="2:29" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:29" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34"/>
+      <c r="B3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="30"/>
+      <c r="D3" s="31"/>
       <c r="E3" s="11" t="s">
         <v>9</v>
       </c>
@@ -1316,10 +1307,10 @@
       </c>
     </row>
     <row r="4" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="34" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="24" t="s">
@@ -1415,8 +1406,8 @@
       </c>
     </row>
     <row r="5" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="43"/>
-      <c r="C5" s="38"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="35"/>
       <c r="D5" s="25" t="s">
         <v>25</v>
       </c>
@@ -1483,7 +1474,7 @@
       <c r="AC5" s="4"/>
     </row>
     <row r="6" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="43"/>
+      <c r="B6" s="40"/>
       <c r="C6" s="9" t="s">
         <v>20</v>
       </c>
@@ -1589,8 +1580,8 @@
       <c r="AC6" s="4"/>
     </row>
     <row r="7" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="43"/>
-      <c r="C7" s="37" t="s">
+      <c r="B7" s="40"/>
+      <c r="C7" s="34" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="24" t="s">
@@ -1686,8 +1677,8 @@
       </c>
     </row>
     <row r="8" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="43"/>
-      <c r="C8" s="38"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="35"/>
       <c r="D8" s="25" t="s">
         <v>25</v>
       </c>
@@ -1754,7 +1745,7 @@
       <c r="AC8" s="4"/>
     </row>
     <row r="9" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="43"/>
+      <c r="B9" s="40"/>
       <c r="C9" s="9" t="s">
         <v>20</v>
       </c>
@@ -1860,8 +1851,8 @@
       <c r="AC9" s="4"/>
     </row>
     <row r="10" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="43"/>
-      <c r="C10" s="37" t="s">
+      <c r="B10" s="40"/>
+      <c r="C10" s="34" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="24" t="s">
@@ -1957,8 +1948,8 @@
       </c>
     </row>
     <row r="11" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="43"/>
-      <c r="C11" s="38"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="35"/>
       <c r="D11" s="25" t="s">
         <v>25</v>
       </c>
@@ -2024,7 +2015,7 @@
       </c>
     </row>
     <row r="12" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="44"/>
+      <c r="B12" s="41"/>
       <c r="C12" s="2" t="s">
         <v>20</v>
       </c>
@@ -2129,11 +2120,11 @@
       </c>
     </row>
     <row r="13" spans="2:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="41"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="38"/>
       <c r="E13" s="15">
         <f>E4+E7+E10</f>
         <v>606065365.68358994</v>
@@ -2232,11 +2223,11 @@
       </c>
     </row>
     <row r="14" spans="2:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="36"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="33"/>
       <c r="E14" s="26">
         <f>E5+E8+E11</f>
         <v>614044688</v>

--- a/2026_dashboard.xlsx
+++ b/2026_dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwchoi\.gemini\antigravity\scratch\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5293809-A5ED-4E61-AA4B-E0C16B9C15EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFF60BD-145C-4B45-BACA-238BB0C7B1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33900" yWindow="1260" windowWidth="25770" windowHeight="13380" xr2:uid="{372AB101-DDC1-4D0A-9680-BFBF2765E290}"/>
+    <workbookView xWindow="31695" yWindow="1275" windowWidth="25770" windowHeight="13380" xr2:uid="{372AB101-DDC1-4D0A-9680-BFBF2765E290}"/>
   </bookViews>
   <sheets>
     <sheet name="매출 데이터" sheetId="2" r:id="rId1"/>
@@ -839,7 +839,7 @@
         <v>732995100</v>
       </c>
       <c r="D7" s="2">
-        <v>32472600</v>
+        <v>49427100</v>
       </c>
       <c r="E7" s="2">
         <v>0</v>
